--- a/data/dividends_info_20260409.xlsx
+++ b/data/dividends_info_20260409.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>32.04999923706055</v>
+        <v>32.68999862670898</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2808112391339149</v>
+        <v>0.275313563110604</v>
       </c>
       <c r="J2" t="n">
         <v>340</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>53.84999847412109</v>
+        <v>53.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.299907186323138</v>
+        <v>1.318267457844002</v>
       </c>
       <c r="J3" t="n">
         <v>319</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.899999618530273</v>
+        <v>8.979999542236328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.674157332266361</v>
+        <v>0.6681514817210997</v>
       </c>
       <c r="J4" t="n">
         <v>249</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>32.05500030517578</v>
+        <v>32.68999862670898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.280767428304994</v>
+        <v>0.275313563110604</v>
       </c>
       <c r="J6" t="n">
         <v>249</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.095000028610229</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I7" t="n">
-        <v>3.675417610904753</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J7" t="n">
         <v>228</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.829999923706055</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I8" t="n">
-        <v>3.430531777311974</v>
+        <v>3.418803474537181</v>
       </c>
       <c r="J8" t="n">
         <v>221</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.800000190734863</v>
+        <v>5.75</v>
       </c>
       <c r="I9" t="n">
-        <v>1.034482724601393</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="J9" t="n">
         <v>193</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>32.05500030517578</v>
+        <v>32.68999862670898</v>
       </c>
       <c r="I11" t="n">
-        <v>0.280767428304994</v>
+        <v>0.275313563110604</v>
       </c>
       <c r="J11" t="n">
         <v>165</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>9.878999710083008</v>
+        <v>9.87600040435791</v>
       </c>
       <c r="I13" t="n">
-        <v>2.631845405710771</v>
+        <v>2.632644687674088</v>
       </c>
       <c r="J13" t="n">
         <v>102</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>16.71999931335449</v>
+        <v>16.78000068664551</v>
       </c>
       <c r="I14" t="n">
-        <v>3.588516893782237</v>
+        <v>3.575685193371384</v>
       </c>
       <c r="J14" t="n">
         <v>102</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18.20000076293945</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="I16" t="n">
-        <v>2.06593397933063</v>
+        <v>2.100558703983215</v>
       </c>
       <c r="J16" t="n">
         <v>102</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.269999980926514</v>
+        <v>5.170000076293945</v>
       </c>
       <c r="I17" t="n">
-        <v>2.277039856438536</v>
+        <v>2.321083137894663</v>
       </c>
       <c r="J17" t="n">
         <v>95</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.140000104904175</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I19" t="n">
-        <v>3.971962422114281</v>
+        <v>4.009434178699683</v>
       </c>
       <c r="J19" t="n">
         <v>88</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>31.64999961853027</v>
+        <v>31</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4739336550013062</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="J21" t="n">
         <v>88</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>23.28000068664551</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="I23" t="n">
-        <v>4.080755893383475</v>
+        <v>4.025423663746726</v>
       </c>
       <c r="J23" t="n">
         <v>74</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.899999976158142</v>
+        <v>1.865000009536743</v>
       </c>
       <c r="I25" t="n">
-        <v>1.736842127057654</v>
+        <v>1.769436988270957</v>
       </c>
       <c r="J25" t="n">
         <v>74</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.460000038146973</v>
+        <v>5.474999904632568</v>
       </c>
       <c r="I26" t="n">
-        <v>5.311355274246863</v>
+        <v>5.296803745231519</v>
       </c>
       <c r="J26" t="n">
         <v>74</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.177999973297119</v>
+        <v>4.184000015258789</v>
       </c>
       <c r="I27" t="n">
-        <v>3.829583557266854</v>
+        <v>3.824091764256451</v>
       </c>
       <c r="J27" t="n">
         <v>74</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.621999979019165</v>
+        <v>2.625999927520752</v>
       </c>
       <c r="I28" t="n">
-        <v>5.286041232229428</v>
+        <v>5.2779894830711</v>
       </c>
       <c r="J28" t="n">
         <v>74</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>56.59999847412109</v>
+        <v>59.43999862670898</v>
       </c>
       <c r="I29" t="n">
-        <v>1.113074234954355</v>
+        <v>1.059892352885946</v>
       </c>
       <c r="J29" t="n">
         <v>74</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>17.70000076293945</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="I30" t="n">
-        <v>4.406779471067463</v>
+        <v>4.297520751480665</v>
       </c>
       <c r="J30" t="n">
         <v>74</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>21.46999931335449</v>
+        <v>21.59000015258789</v>
       </c>
       <c r="I31" t="n">
-        <v>3.959012702302668</v>
+        <v>3.937007846190842</v>
       </c>
       <c r="J31" t="n">
         <v>74</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>32.05500030517578</v>
+        <v>32.68999862670898</v>
       </c>
       <c r="I32" t="n">
-        <v>0.280767428304994</v>
+        <v>0.275313563110604</v>
       </c>
       <c r="J32" t="n">
         <v>74</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6.74399995803833</v>
+        <v>6.808000087738037</v>
       </c>
       <c r="I33" t="n">
-        <v>2.688315556465926</v>
+        <v>2.663043443940921</v>
       </c>
       <c r="J33" t="n">
         <v>74</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>8.149999618530273</v>
+        <v>8.180000305175781</v>
       </c>
       <c r="I34" t="n">
-        <v>3.19018419839984</v>
+        <v>3.178483988998003</v>
       </c>
       <c r="J34" t="n">
         <v>74</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10.19499969482422</v>
+        <v>10.30500030517578</v>
       </c>
       <c r="I35" t="n">
-        <v>2.717018227480938</v>
+        <v>2.688015446839669</v>
       </c>
       <c r="J35" t="n">
         <v>74</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3.910000085830688</v>
+        <v>4.007999897003174</v>
       </c>
       <c r="I36" t="n">
-        <v>2.813299170980203</v>
+        <v>2.744511048571838</v>
       </c>
       <c r="J36" t="n">
         <v>67</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.400000095367432</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9999999602635719</v>
+        <v>0.9448819039544819</v>
       </c>
       <c r="J37" t="n">
         <v>67</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>27.79999923706055</v>
+        <v>28</v>
       </c>
       <c r="I38" t="n">
-        <v>3.99280586497371</v>
+        <v>3.964285714285714</v>
       </c>
       <c r="J38" t="n">
         <v>56</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.8840000033378601</v>
+        <v>0.8889999985694885</v>
       </c>
       <c r="I39" t="n">
-        <v>3.393665145557037</v>
+        <v>3.3745781831579</v>
       </c>
       <c r="J39" t="n">
         <v>53</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.5199999809265137</v>
+        <v>0.5279999971389771</v>
       </c>
       <c r="I40" t="n">
-        <v>4.423077085314424</v>
+        <v>4.356060629664374</v>
       </c>
       <c r="J40" t="n">
         <v>53</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.670000076293945</v>
+        <v>2.660000085830688</v>
       </c>
       <c r="I41" t="n">
-        <v>6.741572841070716</v>
+        <v>6.766917074883777</v>
       </c>
       <c r="J41" t="n">
         <v>46</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8.899999618530273</v>
+        <v>8.5</v>
       </c>
       <c r="I42" t="n">
-        <v>3.370786661331805</v>
+        <v>3.529411764705882</v>
       </c>
       <c r="J42" t="n">
         <v>46</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>12.68000030517578</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="I43" t="n">
-        <v>1.971608785355895</v>
+        <v>1.984126924056797</v>
       </c>
       <c r="J43" t="n">
         <v>46</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>3.470000028610229</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8645533069927757</v>
+        <v>0.8670520135620203</v>
       </c>
       <c r="J44" t="n">
         <v>46</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.559999942779541</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="I45" t="n">
-        <v>4.213483213791417</v>
+        <v>4.166666777045641</v>
       </c>
       <c r="J45" t="n">
         <v>46</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>14.30000019073486</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="I46" t="n">
-        <v>4.055944001845459</v>
+        <v>4.113475066016581</v>
       </c>
       <c r="J46" t="n">
         <v>46</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2.565999984741211</v>
+        <v>2.532000064849854</v>
       </c>
       <c r="I47" t="n">
-        <v>4.053000803524506</v>
+        <v>4.107424855305727</v>
       </c>
       <c r="J47" t="n">
         <v>39</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.041999816894531</v>
+        <v>9.289999961853027</v>
       </c>
       <c r="I48" t="n">
-        <v>3.207255097021228</v>
+        <v>3.121636180740686</v>
       </c>
       <c r="J48" t="n">
         <v>39</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.095000028610229</v>
+        <v>2.079999923706055</v>
       </c>
       <c r="I49" t="n">
-        <v>3.675417610904753</v>
+        <v>3.701923212708811</v>
       </c>
       <c r="J49" t="n">
         <v>39</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>35.88999938964844</v>
+        <v>36.22999954223633</v>
       </c>
       <c r="I50" t="n">
-        <v>4.569518049289843</v>
+        <v>4.526635442233763</v>
       </c>
       <c r="J50" t="n">
         <v>39</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>34.65000152587891</v>
+        <v>34.75</v>
       </c>
       <c r="I51" t="n">
-        <v>5.772005517824489</v>
+        <v>5.755395683453238</v>
       </c>
       <c r="J51" t="n">
         <v>39</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>4.004000186920166</v>
+        <v>4.044000148773193</v>
       </c>
       <c r="I52" t="n">
-        <v>2.4975023809107</v>
+        <v>2.472799117733378</v>
       </c>
       <c r="J52" t="n">
         <v>39</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>36.33000183105469</v>
+        <v>36.54000091552734</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4086429741743013</v>
+        <v>0.4062944616318093</v>
       </c>
       <c r="J53" t="n">
         <v>39</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>22.31999969482422</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I54" t="n">
-        <v>4.121863855640369</v>
+        <v>4.125560679262467</v>
       </c>
       <c r="J54" t="n">
         <v>39</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8.295000076293945</v>
+        <v>8.364999771118164</v>
       </c>
       <c r="I55" t="n">
-        <v>3.616636494764621</v>
+        <v>3.58637188533836</v>
       </c>
       <c r="J55" t="n">
         <v>39</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>79.58000183105469</v>
+        <v>79.66000366210938</v>
       </c>
       <c r="I56" t="n">
-        <v>1.306860990287334</v>
+        <v>1.305548521452906</v>
       </c>
       <c r="J56" t="n">
         <v>39</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>46.5099983215332</v>
+        <v>46.47999954223633</v>
       </c>
       <c r="I57" t="n">
-        <v>1.505052731158483</v>
+        <v>1.506024111217795</v>
       </c>
       <c r="J57" t="n">
         <v>39</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>53.79999923706055</v>
+        <v>53.09999847412109</v>
       </c>
       <c r="I58" t="n">
-        <v>4.089219388844365</v>
+        <v>4.143126296081149</v>
       </c>
       <c r="J58" t="n">
         <v>39</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>7.885000228881836</v>
+        <v>7.934000015258789</v>
       </c>
       <c r="I59" t="n">
-        <v>10.90678471827966</v>
+        <v>10.8394252375351</v>
       </c>
       <c r="J59" t="n">
         <v>39</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>12.01599979400635</v>
+        <v>12.11400032043457</v>
       </c>
       <c r="I60" t="n">
-        <v>4.66045280958919</v>
+        <v>4.622750414290157</v>
       </c>
       <c r="J60" t="n">
         <v>39</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1.924999952316284</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="I61" t="n">
-        <v>2.077922129393791</v>
+        <v>2.051282001121668</v>
       </c>
       <c r="J61" t="n">
         <v>39</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>8.989999771118164</v>
+        <v>9</v>
       </c>
       <c r="I62" t="n">
-        <v>3.337041241800681</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J62" t="n">
         <v>39</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.299999952316284</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I63" t="n">
-        <v>4.695652271263543</v>
+        <v>4.757709291077578</v>
       </c>
       <c r="J63" t="n">
         <v>39</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>71.5</v>
+        <v>72.40000152587891</v>
       </c>
       <c r="I64" t="n">
-        <v>2.881118881118881</v>
+        <v>2.845303807436615</v>
       </c>
       <c r="J64" t="n">
         <v>39</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>15.25</v>
+        <v>15.4399995803833</v>
       </c>
       <c r="I65" t="n">
-        <v>4.918032786885246</v>
+        <v>4.857513085381711</v>
       </c>
       <c r="J65" t="n">
         <v>39</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>16.38999938964844</v>
+        <v>16.20999908447266</v>
       </c>
       <c r="I66" t="n">
-        <v>1.830384448882124</v>
+        <v>1.850709543144675</v>
       </c>
       <c r="J66" t="n">
         <v>39</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>43.90000152587891</v>
+        <v>43.5</v>
       </c>
       <c r="I67" t="n">
-        <v>1.936218611516284</v>
+        <v>1.954022988505747</v>
       </c>
       <c r="J67" t="n">
         <v>39</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>32.91999816894531</v>
+        <v>33.41999816894531</v>
       </c>
       <c r="I68" t="n">
-        <v>2.582017154550869</v>
+        <v>2.543387332647555</v>
       </c>
       <c r="J68" t="n">
         <v>39</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>59.77999877929688</v>
+        <v>60.63999938964844</v>
       </c>
       <c r="I69" t="n">
-        <v>2.17464039234845</v>
+        <v>2.143799493873209</v>
       </c>
       <c r="J69" t="n">
         <v>39</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>7.579999923706055</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I70" t="n">
-        <v>7.915567361993385</v>
+        <v>7.894736941171156</v>
       </c>
       <c r="J70" t="n">
         <v>39</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>5.550000190734863</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I71" t="n">
-        <v>8.468468177435653</v>
+        <v>8.245614311004582</v>
       </c>
       <c r="J71" t="n">
         <v>39</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>5.829999923706055</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I72" t="n">
-        <v>3.430531777311974</v>
+        <v>3.418803474537181</v>
       </c>
       <c r="J72" t="n">
         <v>39</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>22.5</v>
+        <v>22.36000061035156</v>
       </c>
       <c r="I73" t="n">
-        <v>4.444444444444445</v>
+        <v>4.472271792054648</v>
       </c>
       <c r="J73" t="n">
         <v>39</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>4.340000152587891</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="I74" t="n">
-        <v>4.953916876518957</v>
+        <v>4.965358055156295</v>
       </c>
       <c r="J74" t="n">
         <v>39</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>23.85499954223633</v>
+        <v>24.43000030517578</v>
       </c>
       <c r="I75" t="n">
-        <v>1.131838210778219</v>
+        <v>1.105198512595996</v>
       </c>
       <c r="J75" t="n">
         <v>39</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>7.579999923706055</v>
+        <v>7.639999866485596</v>
       </c>
       <c r="I76" t="n">
-        <v>2.638522453997795</v>
+        <v>2.617801092868345</v>
       </c>
       <c r="J76" t="n">
         <v>39</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.720000267028809</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="I77" t="n">
-        <v>2.469135734636793</v>
+        <v>2.487046730438657</v>
       </c>
       <c r="J77" t="n">
         <v>39</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>20.55999946594238</v>
+        <v>20.75</v>
       </c>
       <c r="I78" t="n">
-        <v>3.842412551170705</v>
+        <v>3.80722891566265</v>
       </c>
       <c r="J78" t="n">
         <v>39</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>4.690000057220459</v>
+        <v>4.679999828338623</v>
       </c>
       <c r="I79" t="n">
-        <v>1.982942406510688</v>
+        <v>1.987179560068799</v>
       </c>
       <c r="J79" t="n">
         <v>39</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>5.800000190734863</v>
+        <v>5.75</v>
       </c>
       <c r="I80" t="n">
-        <v>1.034482724601393</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="J80" t="n">
         <v>39</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>36.06000137329102</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="I81" t="n">
-        <v>0.9706045110115792</v>
+        <v>0.9615384212310112</v>
       </c>
       <c r="J81" t="n">
         <v>39</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>7.235000133514404</v>
+        <v>7.40500020980835</v>
       </c>
       <c r="I82" t="n">
-        <v>7.661368206924256</v>
+        <v>7.48548256981543</v>
       </c>
       <c r="J82" t="n">
         <v>39</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>2.079999923706055</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I83" t="n">
-        <v>2.88461549042245</v>
+        <v>2.926829336371755</v>
       </c>
       <c r="J83" t="n">
         <v>39</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>12.55000019073486</v>
+        <v>12.44999980926514</v>
       </c>
       <c r="I84" t="n">
-        <v>1.593625473788053</v>
+        <v>1.606425727421799</v>
       </c>
       <c r="J84" t="n">
         <v>39</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>5.800000190734863</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I85" t="n">
-        <v>1.775862010565724</v>
+        <v>1.769759397972623</v>
       </c>
       <c r="J85" t="n">
         <v>39</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>10.52999973297119</v>
+        <v>10.59500026702881</v>
       </c>
       <c r="I87" t="n">
-        <v>4.10256420660046</v>
+        <v>4.077394894876649</v>
       </c>
       <c r="J87" t="n">
         <v>39</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>26.45000076293945</v>
+        <v>26.6200008392334</v>
       </c>
       <c r="I88" t="n">
-        <v>1.663516020069489</v>
+        <v>1.652892509873681</v>
       </c>
       <c r="J88" t="n">
         <v>39</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1.059999942779541</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="I89" t="n">
-        <v>2.830188832023306</v>
+        <v>2.857142986894471</v>
       </c>
       <c r="J89" t="n">
         <v>39</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>8.090000152587891</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I90" t="n">
-        <v>5.809641423179118</v>
+        <v>5.595238349335005</v>
       </c>
       <c r="J90" t="n">
         <v>39</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>52.93999862670898</v>
+        <v>54.11999893188477</v>
       </c>
       <c r="I91" t="n">
-        <v>2.644503279782255</v>
+        <v>2.586844101312779</v>
       </c>
       <c r="J91" t="n">
         <v>39</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>3.280999898910522</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I92" t="n">
-        <v>9.143554076292929</v>
+        <v>8.771929628875695</v>
       </c>
       <c r="J92" t="n">
         <v>39</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>12.75</v>
+        <v>12.80000019073486</v>
       </c>
       <c r="I93" t="n">
-        <v>0.9411764705882352</v>
+        <v>0.9374999860301615</v>
       </c>
       <c r="J93" t="n">
         <v>39</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3.509999990463257</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I94" t="n">
-        <v>4.843304856464204</v>
+        <v>4.748603453153546</v>
       </c>
       <c r="J94" t="n">
         <v>39</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>19.79999923706055</v>
+        <v>20</v>
       </c>
       <c r="I95" t="n">
-        <v>3.535353671578828</v>
+        <v>3.5</v>
       </c>
       <c r="J95" t="n">
         <v>39</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>2.680000066757202</v>
+        <v>2.660000085830688</v>
       </c>
       <c r="I96" t="n">
-        <v>1.305970116722794</v>
+        <v>1.315789431227401</v>
       </c>
       <c r="J96" t="n">
         <v>39</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>6.179999828338623</v>
+        <v>6.170000076293945</v>
       </c>
       <c r="I97" t="n">
-        <v>5.339805973566092</v>
+        <v>5.348460225598845</v>
       </c>
       <c r="J97" t="n">
         <v>39</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.953000009059906</v>
+        <v>0.9700000286102295</v>
       </c>
       <c r="I98" t="n">
-        <v>7.345225533528802</v>
+        <v>7.216494632509725</v>
       </c>
       <c r="J98" t="n">
         <v>39</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>49.2400016784668</v>
+        <v>48.70000076293945</v>
       </c>
       <c r="I99" t="n">
-        <v>1.44191709138485</v>
+        <v>1.457905521308139</v>
       </c>
       <c r="J99" t="n">
         <v>39</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>80.5</v>
+        <v>79.30000305175781</v>
       </c>
       <c r="I100" t="n">
-        <v>1.677018633540373</v>
+        <v>1.702395899176545</v>
       </c>
       <c r="J100" t="n">
         <v>39</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>7.139999866485596</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I101" t="n">
-        <v>1.120448200223526</v>
+        <v>1.111111140545505</v>
       </c>
       <c r="J101" t="n">
         <v>39</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.017</v>
+        <v>3</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>3.019999980926514</v>
+        <v>254</v>
       </c>
       <c r="I102" t="n">
-        <v>0.5629139108399771</v>
+        <v>1.181102362204724</v>
       </c>
       <c r="J102" t="n">
         <v>39</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>2.849999904632568</v>
+        <v>4.188000202178955</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3508772047235992</v>
+        <v>4.059216613971305</v>
       </c>
       <c r="J103" t="n">
         <v>39</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1.12</v>
+        <v>0.297</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>21.34000015258789</v>
+        <v>7.449999809265137</v>
       </c>
       <c r="I104" t="n">
-        <v>5.248359850007678</v>
+        <v>3.986577283272386</v>
       </c>
       <c r="J104" t="n">
         <v>39</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.1</v>
+        <v>0.45</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>1.340000033378601</v>
+        <v>59.29999923706055</v>
       </c>
       <c r="I105" t="n">
-        <v>7.462686381273111</v>
+        <v>0.7588532981274725</v>
       </c>
       <c r="J105" t="n">
         <v>39</v>
@@ -5379,11 +5379,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0003865570</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>2.549999952316284</v>
+        <v>4.909999847412109</v>
       </c>
       <c r="I106" t="n">
-        <v>10.19607862203408</v>
+        <v>0.8146639764374455</v>
       </c>
       <c r="J106" t="n">
         <v>39</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2.130000114440918</v>
+        <v>32.18000030517578</v>
       </c>
       <c r="I107" t="n">
-        <v>4.333333100511447</v>
+        <v>3.262896177882011</v>
       </c>
       <c r="J107" t="n">
         <v>39</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5486,12 +5486,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5501,30 +5501,30 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>9.5</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I108" t="n">
-        <v>3.684210526315789</v>
+        <v>3.225806550850609</v>
       </c>
       <c r="J108" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K108" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.096</v>
+        <v>0.38</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5533,12 +5533,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5548,44 +5548,44 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>4.800000190734863</v>
+        <v>18.96999931335449</v>
       </c>
       <c r="I109" t="n">
-        <v>1.999999920527144</v>
+        <v>2.003162961279012</v>
       </c>
       <c r="J109" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K109" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5595,30 +5595,30 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>6</v>
+        <v>25.68000030517578</v>
       </c>
       <c r="I110" t="n">
-        <v>5</v>
+        <v>2.336448570364972</v>
       </c>
       <c r="J110" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K110" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5642,30 +5642,30 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>11.89999961853027</v>
+        <v>29.85000038146973</v>
       </c>
       <c r="I111" t="n">
-        <v>1.680672322783665</v>
+        <v>1.172529298248428</v>
       </c>
       <c r="J111" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K111" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.06</v>
+        <v>0.017</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5674,45 +5674,45 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>8.899999618530273</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="I112" t="n">
-        <v>0.674157332266361</v>
+        <v>0.5704697950064269</v>
       </c>
       <c r="J112" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K112" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5736,30 +5736,30 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>2.200000047683716</v>
+        <v>2.825000047683716</v>
       </c>
       <c r="I113" t="n">
-        <v>2.727272668160684</v>
+        <v>0.3539822949100208</v>
       </c>
       <c r="J113" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K113" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5</v>
+        <v>1.12</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5783,26 +5783,26 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>16.15999984741211</v>
+        <v>21.48999977111816</v>
       </c>
       <c r="I114" t="n">
-        <v>3.094059435155693</v>
+        <v>5.211726439872942</v>
       </c>
       <c r="J114" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K114" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5830,30 +5830,30 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>3.920000076293945</v>
+        <v>1.330000042915344</v>
       </c>
       <c r="I115" t="n">
-        <v>2.551020358513417</v>
+        <v>7.518796749870864</v>
       </c>
       <c r="J115" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K115" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5862,12 +5862,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5877,30 +5877,30 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>IT0003865570</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>9.399999618530273</v>
+        <v>2.563999891281128</v>
       </c>
       <c r="I116" t="n">
-        <v>0.9042553558453239</v>
+        <v>10.14040604619872</v>
       </c>
       <c r="J116" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K116" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.095</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5909,12 +5909,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5924,30 +5924,30 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.539999961853027</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I117" t="n">
-        <v>2.092511030798009</v>
+        <v>4.416268123948006</v>
       </c>
       <c r="J117" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K117" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.03</v>
+        <v>0.095</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1.129999995231628</v>
+        <v>4.519999980926514</v>
       </c>
       <c r="I118" t="n">
-        <v>2.654867267840171</v>
+        <v>2.101769920373469</v>
       </c>
       <c r="J118" t="n">
         <v>32</v>
@@ -5990,11 +5990,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6018,14 +6018,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.699999809265137</v>
+        <v>1.129999995231628</v>
       </c>
       <c r="I119" t="n">
-        <v>1.168831197784008</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J119" t="n">
         <v>32</v>
@@ -6037,11 +6037,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>7.949999809265137</v>
+        <v>7.699999809265137</v>
       </c>
       <c r="I120" t="n">
-        <v>1.2578616653985</v>
+        <v>1.168831197784008</v>
       </c>
       <c r="J120" t="n">
         <v>32</v>
@@ -6084,11 +6084,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6112,14 +6112,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>7.079999923706055</v>
+        <v>7.949999809265137</v>
       </c>
       <c r="I121" t="n">
-        <v>3.107344666253049</v>
+        <v>1.2578616653985</v>
       </c>
       <c r="J121" t="n">
         <v>32</v>
@@ -6131,11 +6131,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6159,30 +6159,30 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0004093263</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>3.549999952316284</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="I122" t="n">
-        <v>4.507042314059866</v>
+        <v>3.089887690113706</v>
       </c>
       <c r="J122" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K122" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.61</v>
+        <v>0.16</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6206,14 +6206,14 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0004093263</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>22.79999923706055</v>
+        <v>3.605000019073486</v>
       </c>
       <c r="I123" t="n">
-        <v>2.675438686017444</v>
+        <v>4.438280142953266</v>
       </c>
       <c r="J123" t="n">
         <v>25</v>
@@ -6225,11 +6225,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.15</v>
+        <v>0.61</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6253,14 +6253,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>3.039999961853027</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I124" t="n">
-        <v>4.934210588231972</v>
+        <v>2.675438686017444</v>
       </c>
       <c r="J124" t="n">
         <v>25</v>
@@ -6272,11 +6272,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6300,14 +6300,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>11.80000019073486</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I125" t="n">
-        <v>5.932203293942543</v>
+        <v>4.934210588231972</v>
       </c>
       <c r="J125" t="n">
         <v>25</v>
@@ -6319,11 +6319,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5105</v>
+        <v>0.7</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6347,14 +6347,14 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>9.069999694824219</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="I126" t="n">
-        <v>5.628445613855048</v>
+        <v>5.907172805619612</v>
       </c>
       <c r="J126" t="n">
         <v>25</v>
@@ -6366,15 +6366,15 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.27</v>
+        <v>0.5105</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6394,14 +6394,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>8.225000381469727</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="I127" t="n">
-        <v>3.28267461978833</v>
+        <v>5.597587789538714</v>
       </c>
       <c r="J127" t="n">
         <v>25</v>
@@ -6413,15 +6413,15 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6441,14 +6441,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>5.324999809265137</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>6.572770188480079</v>
+        <v>3.288672335511219</v>
       </c>
       <c r="J128" t="n">
         <v>25</v>
@@ -6460,11 +6460,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.1</v>
+        <v>0.35</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6488,14 +6488,14 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>37.40000152587891</v>
+        <v>5.315000057220459</v>
       </c>
       <c r="I129" t="n">
-        <v>2.941176350591472</v>
+        <v>6.585136335502441</v>
       </c>
       <c r="J129" t="n">
         <v>25</v>
@@ -6507,11 +6507,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6530,19 +6530,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>18.64999961853027</v>
+        <v>37.20000076293945</v>
       </c>
       <c r="I130" t="n">
-        <v>4.021447803434884</v>
+        <v>2.956989186666567</v>
       </c>
       <c r="J130" t="n">
         <v>25</v>
@@ -6554,11 +6554,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.43</v>
+        <v>0.75</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6577,19 +6577,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>10.39999961853027</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I131" t="n">
-        <v>4.134615536272179</v>
+        <v>4.032257981818046</v>
       </c>
       <c r="J131" t="n">
         <v>25</v>
@@ -6601,11 +6601,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6629,14 +6629,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>4.190000057220459</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I132" t="n">
-        <v>3.57995221841372</v>
+        <v>4.154589218855071</v>
       </c>
       <c r="J132" t="n">
         <v>25</v>
@@ -6648,11 +6648,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.197169</v>
+        <v>0.15</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6676,14 +6676,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>12.0600004196167</v>
+        <v>4.170000076293945</v>
       </c>
       <c r="I133" t="n">
-        <v>1.634900440627568</v>
+        <v>3.597122236345648</v>
       </c>
       <c r="J133" t="n">
         <v>25</v>
@@ -6695,11 +6695,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1.1</v>
+        <v>0.197169</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6723,14 +6723,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>28.45000076293945</v>
+        <v>12.11999988555908</v>
       </c>
       <c r="I134" t="n">
-        <v>3.866432233748553</v>
+        <v>1.626806946053901</v>
       </c>
       <c r="J134" t="n">
         <v>25</v>
@@ -6742,11 +6742,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>19.65999984741211</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="I135" t="n">
-        <v>2.543235014652435</v>
+        <v>3.846153794853453</v>
       </c>
       <c r="J135" t="n">
         <v>25</v>
@@ -6789,11 +6789,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6817,14 +6817,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>42.45000076293945</v>
+        <v>19.57999992370605</v>
       </c>
       <c r="I136" t="n">
-        <v>1.107184903540282</v>
+        <v>2.553626159082033</v>
       </c>
       <c r="J136" t="n">
         <v>25</v>
@@ -6836,11 +6836,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.11</v>
+        <v>0.47</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>2.539999961853027</v>
+        <v>43.34999847412109</v>
       </c>
       <c r="I137" t="n">
-        <v>4.330708726458042</v>
+        <v>1.084198423399204</v>
       </c>
       <c r="J137" t="n">
         <v>25</v>
@@ -6883,11 +6883,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.2</v>
+        <v>0.11</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6911,14 +6911,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>76.19999694824219</v>
+        <v>2.579999923706055</v>
       </c>
       <c r="I138" t="n">
-        <v>1.574803212676089</v>
+        <v>4.263566017552043</v>
       </c>
       <c r="J138" t="n">
         <v>25</v>
@@ -6930,11 +6930,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.27</v>
+        <v>1.2</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -6958,14 +6958,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>23.45000076293945</v>
+        <v>78.59999847412109</v>
       </c>
       <c r="I139" t="n">
-        <v>1.1513858900453</v>
+        <v>1.526717586890409</v>
       </c>
       <c r="J139" t="n">
         <v>25</v>
@@ -6977,11 +6977,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7005,14 +7005,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>10.35000038146973</v>
+        <v>23.5</v>
       </c>
       <c r="I140" t="n">
-        <v>3.671497449220761</v>
+        <v>1.148936170212766</v>
       </c>
       <c r="J140" t="n">
         <v>25</v>
@@ -7024,11 +7024,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>27.45000076293945</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="I141" t="n">
-        <v>1.092896144487665</v>
+        <v>3.636363702735056</v>
       </c>
       <c r="J141" t="n">
         <v>25</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>0.153999999165535</v>
+        <v>0.1519999951124191</v>
       </c>
       <c r="I142" t="n">
-        <v>4.545454570084565</v>
+        <v>4.605263305977611</v>
       </c>
       <c r="J142" t="n">
         <v>18</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>7</v>
+        <v>7.170000076293945</v>
       </c>
       <c r="I143" t="n">
-        <v>2.285714285714286</v>
+        <v>2.231520199407046</v>
       </c>
       <c r="J143" t="n">
         <v>18</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>2.204999923706055</v>
+        <v>2.184999942779541</v>
       </c>
       <c r="I144" t="n">
-        <v>2.947845906985394</v>
+        <v>2.974828453190412</v>
       </c>
       <c r="J144" t="n">
         <v>18</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>7.78000020980835</v>
+        <v>7.769999980926514</v>
       </c>
       <c r="I145" t="n">
-        <v>3.213367522597515</v>
+        <v>3.217503225401416</v>
       </c>
       <c r="J145" t="n">
         <v>18</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1.379999995231628</v>
+        <v>1.370000004768372</v>
       </c>
       <c r="I146" t="n">
-        <v>5.072463785643038</v>
+        <v>5.109489033310991</v>
       </c>
       <c r="J146" t="n">
         <v>18</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>6.739999771118164</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="I147" t="n">
-        <v>7.418397878032125</v>
+        <v>7.385524393038065</v>
       </c>
       <c r="J147" t="n">
         <v>11</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>18.5</v>
+        <v>18.29999923706055</v>
       </c>
       <c r="I148" t="n">
-        <v>3.513513513513514</v>
+        <v>3.551912716387669</v>
       </c>
       <c r="J148" t="n">
         <v>11</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>12.57999992370605</v>
+        <v>12.625</v>
       </c>
       <c r="I149" t="n">
-        <v>4.292527847972487</v>
+        <v>4.277227722772277</v>
       </c>
       <c r="J149" t="n">
         <v>11</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>6.52400016784668</v>
+        <v>6.616000175476074</v>
       </c>
       <c r="I150" t="n">
-        <v>1.53280192255124</v>
+        <v>1.511487263417495</v>
       </c>
       <c r="J150" t="n">
         <v>11</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>8.319999694824219</v>
+        <v>8.260000228881836</v>
       </c>
       <c r="I151" t="n">
-        <v>1.923076993614967</v>
+        <v>1.93704595116772</v>
       </c>
       <c r="J151" t="n">
         <v>11</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>296.5</v>
+        <v>300.3500061035156</v>
       </c>
       <c r="I152" t="n">
-        <v>1.219224283305228</v>
+        <v>1.203595780435606</v>
       </c>
       <c r="J152" t="n">
         <v>11</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>27.39999961853027</v>
+        <v>28</v>
       </c>
       <c r="I153" t="n">
-        <v>4.96350371873819</v>
+        <v>4.857142857142858</v>
       </c>
       <c r="J153" t="n">
         <v>11</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>14.68000030517578</v>
+        <v>14.85999965667725</v>
       </c>
       <c r="I154" t="n">
-        <v>3.985013541135584</v>
+        <v>3.936743025004943</v>
       </c>
       <c r="J154" t="n">
         <v>11</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>17.64999961853027</v>
+        <v>17.67000007629395</v>
       </c>
       <c r="I155" t="n">
-        <v>3.569405176295751</v>
+        <v>3.565365010072679</v>
       </c>
       <c r="J155" t="n">
         <v>11</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>114.3000030517578</v>
+        <v>115.5999984741211</v>
       </c>
       <c r="I156" t="n">
-        <v>0.7874015537798876</v>
+        <v>0.7785467230793082</v>
       </c>
       <c r="J156" t="n">
         <v>11</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>66.91999816894531</v>
+        <v>66.88999938964844</v>
       </c>
       <c r="I157" t="n">
-        <v>2.571428641787604</v>
+        <v>2.572581874273873</v>
       </c>
       <c r="J157" t="n">
         <v>11</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>24.79999923706055</v>
+        <v>25</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5645161463988565</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J158" t="n">
         <v>4</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>1.570000052452087</v>
+        <v>1.539999961853027</v>
       </c>
       <c r="I159" t="n">
-        <v>3.821655923277815</v>
+        <v>3.896103992613359</v>
       </c>
       <c r="J159" t="n">
         <v>4</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>1.899999976158142</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I160" t="n">
-        <v>1.789473706665462</v>
+        <v>1.770833372914544</v>
       </c>
       <c r="J160" t="n">
         <v>-10</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>23.86000061035156</v>
+        <v>24.43000030517578</v>
       </c>
       <c r="I161" t="n">
-        <v>1.089689829627247</v>
+        <v>1.0642652343517</v>
       </c>
       <c r="J161" t="n">
         <v>-17</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>32.05500030517578</v>
+        <v>32.68999862670898</v>
       </c>
       <c r="I162" t="n">
-        <v>0.280767428304994</v>
+        <v>0.275313563110604</v>
       </c>
       <c r="J162" t="n">
         <v>-17</v>
@@ -8066,7 +8066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C552"/>
+  <dimension ref="A1:C542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8225,7 +8225,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -8242,7 +8242,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8252,14 +8252,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8269,14 +8269,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8286,14 +8286,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8303,14 +8303,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8320,14 +8320,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8371,14 +8371,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8388,14 +8388,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8405,14 +8405,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8582,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -8718,7 +8718,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -8728,14 +8728,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8752,7 +8752,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8837,7 +8837,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -8847,14 +8847,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8898,14 +8898,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8915,14 +8915,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8939,7 +8939,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -8956,7 +8956,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8966,14 +8966,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8983,14 +8983,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9000,14 +9000,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9041,7 +9041,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9058,7 +9058,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9068,14 +9068,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9109,7 +9109,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9119,14 +9119,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9143,7 +9143,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -9160,7 +9160,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -9170,14 +9170,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -9187,14 +9187,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -9211,7 +9211,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9228,7 +9228,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9245,7 +9245,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -9262,7 +9262,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9279,7 +9279,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -9289,14 +9289,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9313,7 +9313,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9323,14 +9323,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9340,14 +9340,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9425,14 +9425,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9459,14 +9459,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9483,7 +9483,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9500,7 +9500,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9517,7 +9517,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9534,7 +9534,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9551,7 +9551,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9561,14 +9561,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9578,14 +9578,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9602,7 +9602,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9612,14 +9612,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9629,14 +9629,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9646,14 +9646,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9663,14 +9663,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9680,14 +9680,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9704,7 +9704,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9731,14 +9731,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9772,7 +9772,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9891,7 +9891,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9908,7 +9908,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9925,7 +9925,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9942,7 +9942,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9959,7 +9959,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9976,7 +9976,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9993,7 +9993,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10010,7 +10010,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10027,7 +10027,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10044,7 +10044,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10061,7 +10061,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10078,7 +10078,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10095,7 +10095,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10129,7 +10129,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10146,7 +10146,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10163,7 +10163,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10173,14 +10173,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10190,14 +10190,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10207,14 +10207,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10224,14 +10224,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10248,7 +10248,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10265,7 +10265,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10282,7 +10282,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10299,7 +10299,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10316,7 +10316,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10350,7 +10350,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10367,7 +10367,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10384,7 +10384,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10401,7 +10401,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10411,14 +10411,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10435,7 +10435,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10445,14 +10445,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10469,7 +10469,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10486,7 +10486,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10503,7 +10503,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10513,14 +10513,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10530,14 +10530,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10554,7 +10554,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10571,7 +10571,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10581,14 +10581,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10598,14 +10598,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10615,14 +10615,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10632,14 +10632,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10649,14 +10649,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10666,14 +10666,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10683,14 +10683,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10700,14 +10700,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10724,7 +10724,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10734,14 +10734,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10758,7 +10758,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10768,14 +10768,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10792,7 +10792,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10826,7 +10826,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10843,7 +10843,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10860,7 +10860,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10877,7 +10877,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10894,7 +10894,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10911,7 +10911,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10928,7 +10928,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10945,7 +10945,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10962,7 +10962,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10996,7 +10996,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11013,7 +11013,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11030,7 +11030,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11047,7 +11047,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11057,14 +11057,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11074,14 +11074,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11098,7 +11098,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11115,7 +11115,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11125,14 +11125,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11149,7 +11149,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11166,7 +11166,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11183,7 +11183,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11193,14 +11193,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11210,14 +11210,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11234,7 +11234,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11251,7 +11251,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11268,7 +11268,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11285,7 +11285,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11302,7 +11302,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11319,7 +11319,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11336,7 +11336,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11346,14 +11346,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11370,7 +11370,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11387,7 +11387,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11404,7 +11404,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11421,7 +11421,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11438,7 +11438,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11455,7 +11455,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11472,7 +11472,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11489,7 +11489,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11499,14 +11499,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11523,7 +11523,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -11533,14 +11533,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -11550,14 +11550,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -11567,14 +11567,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -11591,7 +11591,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -11608,7 +11608,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11625,7 +11625,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -11635,14 +11635,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11659,7 +11659,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -11676,7 +11676,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11693,7 +11693,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11710,7 +11710,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11727,7 +11727,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11737,14 +11737,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11754,14 +11754,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11771,14 +11771,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11795,7 +11795,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11812,7 +11812,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11863,7 +11863,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11880,7 +11880,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11897,7 +11897,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11914,7 +11914,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11931,7 +11931,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -11948,7 +11948,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -11965,7 +11965,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -11982,7 +11982,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -11992,14 +11992,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12009,14 +12009,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12033,7 +12033,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12050,7 +12050,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12067,7 +12067,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12084,7 +12084,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12101,7 +12101,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12111,14 +12111,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12135,7 +12135,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12152,7 +12152,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12169,7 +12169,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12186,7 +12186,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12196,14 +12196,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12220,7 +12220,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12230,14 +12230,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12271,7 +12271,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12288,7 +12288,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12305,7 +12305,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12322,7 +12322,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12339,7 +12339,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12356,7 +12356,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12373,7 +12373,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12390,7 +12390,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12407,7 +12407,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12417,14 +12417,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -12441,7 +12441,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -12458,7 +12458,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -12475,7 +12475,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -12492,7 +12492,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -12502,14 +12502,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -12526,7 +12526,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -12536,14 +12536,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -12560,7 +12560,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12577,7 +12577,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -12594,7 +12594,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12611,7 +12611,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -12628,7 +12628,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12638,14 +12638,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12662,7 +12662,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12672,14 +12672,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -12689,14 +12689,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12713,7 +12713,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -12723,14 +12723,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12740,14 +12740,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12764,7 +12764,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12781,7 +12781,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -12798,7 +12798,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12808,14 +12808,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -12832,7 +12832,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12842,14 +12842,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -12859,14 +12859,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12883,7 +12883,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12900,7 +12900,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12917,7 +12917,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12934,7 +12934,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12951,7 +12951,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12985,7 +12985,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13002,7 +13002,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13019,7 +13019,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13036,7 +13036,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13053,7 +13053,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13070,7 +13070,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13087,7 +13087,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13104,7 +13104,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13121,7 +13121,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13138,7 +13138,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13155,7 +13155,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13172,7 +13172,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13182,14 +13182,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13199,14 +13199,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13216,14 +13216,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13274,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13284,14 +13284,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13308,7 +13308,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13325,7 +13325,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13342,7 +13342,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13359,7 +13359,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13376,7 +13376,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13386,14 +13386,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13410,7 +13410,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13420,14 +13420,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -13444,7 +13444,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13461,7 +13461,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13478,7 +13478,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13495,7 +13495,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -13512,7 +13512,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -13529,7 +13529,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -13546,7 +13546,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -13556,14 +13556,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -13580,7 +13580,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -13597,7 +13597,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -13614,7 +13614,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13648,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -13665,7 +13665,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -13699,7 +13699,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -13716,7 +13716,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -13733,7 +13733,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -13750,7 +13750,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -13767,7 +13767,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -13784,7 +13784,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -13794,14 +13794,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -13818,7 +13818,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -13835,7 +13835,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -13852,7 +13852,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -13862,14 +13862,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13886,7 +13886,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13896,14 +13896,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13913,14 +13913,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13937,7 +13937,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -13954,7 +13954,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -13971,7 +13971,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -13988,7 +13988,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14005,7 +14005,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14022,7 +14022,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14032,14 +14032,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14049,14 +14049,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14073,7 +14073,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14090,7 +14090,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14107,7 +14107,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14124,7 +14124,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14141,7 +14141,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14158,7 +14158,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14175,7 +14175,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14192,7 +14192,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -14226,7 +14226,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14243,7 +14243,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14260,7 +14260,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14277,7 +14277,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14294,7 +14294,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14311,7 +14311,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14321,14 +14321,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14345,7 +14345,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14362,7 +14362,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14379,7 +14379,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14413,7 +14413,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14430,7 +14430,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14447,7 +14447,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14464,7 +14464,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -14474,14 +14474,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -14498,7 +14498,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -14515,7 +14515,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -14532,7 +14532,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -14549,7 +14549,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -14566,7 +14566,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -14583,7 +14583,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -14600,7 +14600,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -14610,14 +14610,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -14627,14 +14627,14 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -14651,7 +14651,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -14668,7 +14668,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -14678,14 +14678,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -14702,7 +14702,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -14719,7 +14719,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -14736,7 +14736,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -14753,7 +14753,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -14763,14 +14763,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -14787,7 +14787,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -14804,7 +14804,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -14814,14 +14814,14 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -14831,14 +14831,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -14855,7 +14855,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -14872,7 +14872,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -14889,7 +14889,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -14906,7 +14906,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -14916,14 +14916,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -14940,7 +14940,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -14957,7 +14957,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -14974,7 +14974,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -14991,7 +14991,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15008,7 +15008,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15025,7 +15025,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15042,7 +15042,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15052,14 +15052,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15076,7 +15076,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15093,7 +15093,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15127,12 +15127,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -15161,29 +15161,29 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -15195,12 +15195,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -15212,46 +15212,46 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -15263,12 +15263,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -15280,24 +15280,24 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15307,14 +15307,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15331,7 +15331,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -15348,7 +15348,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -15358,14 +15358,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15382,7 +15382,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -15392,14 +15392,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -15416,7 +15416,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -15426,14 +15426,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -15450,46 +15450,46 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -15501,29 +15501,29 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -15535,12 +15535,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -15552,75 +15552,75 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -15630,14 +15630,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -15647,14 +15647,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -15671,7 +15671,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -15688,7 +15688,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -15705,7 +15705,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -15715,14 +15715,14 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -15739,7 +15739,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -15749,14 +15749,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -15766,14 +15766,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -15790,7 +15790,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -15800,14 +15800,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -15841,7 +15841,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -15851,14 +15851,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -15868,14 +15868,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -15892,7 +15892,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -15909,46 +15909,46 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -15960,46 +15960,46 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -16011,46 +16011,46 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -16062,12 +16062,12 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -16079,7 +16079,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16089,14 +16089,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16106,14 +16106,14 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16123,14 +16123,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16140,14 +16140,14 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16157,14 +16157,14 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16198,7 +16198,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16208,14 +16208,14 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16232,7 +16232,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16242,14 +16242,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16266,7 +16266,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16283,7 +16283,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16300,7 +16300,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16310,14 +16310,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16334,12 +16334,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -16351,29 +16351,29 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -16385,46 +16385,46 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -16436,12 +16436,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -16453,12 +16453,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -16470,41 +16470,41 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -16521,7 +16521,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -16531,14 +16531,14 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -16548,14 +16548,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -16565,14 +16565,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -16582,14 +16582,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -16599,14 +16599,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -16616,14 +16616,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -16633,14 +16633,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -16650,14 +16650,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -16674,7 +16674,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -16684,14 +16684,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -16708,7 +16708,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -16718,14 +16718,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -16735,14 +16735,14 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -16759,7 +16759,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -16776,7 +16776,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -16786,14 +16786,14 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -16803,14 +16803,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -16820,14 +16820,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -16837,14 +16837,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -16854,14 +16854,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -16871,14 +16871,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -16888,14 +16888,14 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -16912,7 +16912,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -16922,14 +16922,14 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -16946,7 +16946,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -16956,14 +16956,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -16973,14 +16973,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17014,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17031,7 +17031,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17041,14 +17041,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17065,7 +17065,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17075,14 +17075,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17099,12 +17099,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -17116,131 +17116,131 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -17252,24 +17252,24 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17278,176 +17278,6 @@
         </is>
       </c>
       <c r="C542" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C547" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>Litix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C548" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>DiaSorin S.p.A</t>
-        </is>
-      </c>
-      <c r="B549" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C549" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C551" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
         <is>
           <t>Additional Periodic Financial Information</t>
         </is>
@@ -17464,230 +17294,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0004587470</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.4740000069141388</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8438818442305566</v>
-      </c>
-      <c r="I2" t="n">
-        <v>102</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0004587470</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-08-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.4740000069141388</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.8438818442305566</v>
-      </c>
-      <c r="I3" t="n">
-        <v>137</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0004587470</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-10-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.4740000069141388</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.8438818442305566</v>
-      </c>
-      <c r="I4" t="n">
-        <v>193</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0004587470</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-12-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-12-16</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.4740000069141388</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.8438818442305566</v>
-      </c>
-      <c r="I5" t="n">
-        <v>249</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17698,282 +17307,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DiaSorin S.p.A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EXPERT.AI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Friends S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Litix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Nusco S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TESMEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>